--- a/artfynd/A 28659-2025 artfynd.xlsx
+++ b/artfynd/A 28659-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126112407</v>
       </c>
       <c r="B2" t="n">
-        <v>98243</v>
+        <v>98245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126111570</v>
       </c>
       <c r="B3" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126111198</v>
       </c>
       <c r="B4" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126111855</v>
       </c>
       <c r="B5" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126112602</v>
       </c>
       <c r="B6" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126111960</v>
       </c>
       <c r="B7" t="n">
-        <v>75067</v>
+        <v>75068</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126111060</v>
       </c>
       <c r="B8" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28659-2025 artfynd.xlsx
+++ b/artfynd/A 28659-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126112407</v>
       </c>
       <c r="B2" t="n">
-        <v>98245</v>
+        <v>98247</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126111060</v>
       </c>
       <c r="B8" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28659-2025 artfynd.xlsx
+++ b/artfynd/A 28659-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126112407</v>
       </c>
       <c r="B2" t="n">
-        <v>98247</v>
+        <v>98249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126111060</v>
       </c>
       <c r="B8" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28659-2025 artfynd.xlsx
+++ b/artfynd/A 28659-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126112407</v>
       </c>
       <c r="B2" t="n">
-        <v>98249</v>
+        <v>98253</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126111570</v>
       </c>
       <c r="B3" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126111198</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126111855</v>
       </c>
       <c r="B5" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126112602</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126111960</v>
       </c>
       <c r="B7" t="n">
-        <v>75068</v>
+        <v>75072</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126111060</v>
       </c>
       <c r="B8" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28659-2025 artfynd.xlsx
+++ b/artfynd/A 28659-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126112407</v>
       </c>
       <c r="B2" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126111060</v>
       </c>
       <c r="B8" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28659-2025 artfynd.xlsx
+++ b/artfynd/A 28659-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126112407</v>
       </c>
       <c r="B2" t="n">
-        <v>98256</v>
+        <v>98265</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126111570</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126111198</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126111855</v>
       </c>
       <c r="B5" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126112602</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126111960</v>
       </c>
       <c r="B7" t="n">
-        <v>75072</v>
+        <v>75075</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126111060</v>
       </c>
       <c r="B8" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
